--- a/ver7/tree.xlsx
+++ b/ver7/tree.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mini\Documents\25\project\tree2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\i7\drevo2\album1\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="8610"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="8580" tabRatio="673"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,8 @@
     <sheet name="foto_item" sheetId="10" r:id="rId9"/>
     <sheet name="language" sheetId="8" r:id="rId10"/>
     <sheet name="help" sheetId="9" r:id="rId11"/>
-    <sheet name="version" sheetId="12" r:id="rId12"/>
+    <sheet name="preSet" sheetId="13" r:id="rId12"/>
+    <sheet name="version" sheetId="12" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">language!$A$1:$L$69</definedName>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="336">
   <si>
     <t>idA</t>
   </si>
@@ -705,9 +706,6 @@
     <t>description</t>
   </si>
   <si>
-    <t>v_0.01</t>
-  </si>
-  <si>
     <t>Кононов Андрей Николаевич</t>
   </si>
   <si>
@@ -726,9 +724,6 @@
     <t>1984</t>
   </si>
   <si>
-    <t>~1941</t>
-  </si>
-  <si>
     <t>~1893</t>
   </si>
   <si>
@@ -1027,6 +1022,27 @@
   </si>
   <si>
     <t>Обозова_Ульяна</t>
+  </si>
+  <si>
+    <t>preSet</t>
+  </si>
+  <si>
+    <t>~1943</t>
+  </si>
+  <si>
+    <t>КО</t>
+  </si>
+  <si>
+    <t>v_0.02</t>
+  </si>
+  <si>
+    <t>Все ветви</t>
+  </si>
+  <si>
+    <t>Кононовы-Обозовы</t>
+  </si>
+  <si>
+    <t>ver7, preset</t>
   </si>
 </sst>
 </file>
@@ -1419,7 +1435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.85546875" style="5" customWidth="1"/>
@@ -1442,7 +1458,7 @@
     <col min="19" max="19" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1500,559 +1516,632 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T1" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="str">
         <f t="shared" ref="A2:A4" si="0">SUBSTITUTE(B2, " ", "_")</f>
         <v>Обозов_Никита</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T2" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Обозова_Ульяна</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T3" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Обозова_Татьяна</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+      <c r="T4" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="str">
         <f t="shared" ref="A5:A25" si="1">SUBSTITUTE(B5, " ", "_")</f>
         <v>Обозов_Михаил_Никититич</v>
       </c>
       <c r="B5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="P5" s="10"/>
-    </row>
-    <row r="6" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T5" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Агафья_Ивановна</v>
       </c>
       <c r="B6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P6" s="10" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+      <c r="T6" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Кононов_Спиридон</v>
       </c>
       <c r="B7" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="10"/>
       <c r="Q7" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Кононов_Николай_Спиридонович</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+      <c r="T8" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Кононов_Михаил_Спиридонович</v>
       </c>
       <c r="B9" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+      <c r="T9" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Кононов_Иван_Николаевич</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+      <c r="T10" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Леонтьева_Мария_Петровна</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="10" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+      <c r="T11" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Леонтьева</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
-    </row>
-    <row r="13" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T12" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Сухарникова_Акулина</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E13" s="2"/>
       <c r="O13" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+      <c r="T13" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Кононов_Василий_Николаевич</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+      <c r="T14" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Кононова_Устинья_Николаевна</v>
       </c>
       <c r="B15" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+      <c r="T15" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f t="shared" si="1"/>
         <v>Кононов_Андрей_Николаевич</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>230</v>
+        <v>330</v>
       </c>
       <c r="O16"/>
       <c r="P16"/>
       <c r="Q16"/>
       <c r="R16"/>
-    </row>
-    <row r="17" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T16" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f t="shared" si="1"/>
         <v>Обозова_Прасковья_Михайловна</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="G17" s="2" t="s">
+      <c r="I17" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>228</v>
       </c>
       <c r="K17"/>
       <c r="O17" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="P17"/>
       <c r="R17"/>
-    </row>
-    <row r="18" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T17" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>SUBSTITUTE(B18, " ", "_")</f>
         <v>Кононова_Анна_Андреевна</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F18" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G18" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="J18" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="O18" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="P18"/>
       <c r="R18"/>
-    </row>
-    <row r="19" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T18" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f t="shared" si="1"/>
         <v>Кононова_Клавдия_Андреевна</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G19" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="J19" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="O19" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="P19"/>
       <c r="R19"/>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="T19" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Кононова_Александра_Андреевна</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G20" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="J20" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>262</v>
       </c>
       <c r="K20"/>
       <c r="O20" s="5" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+      <c r="T20" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Кононов_Николай_Андреевич</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21"/>
       <c r="O21" s="5" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+      <c r="T21" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Обозова_Ольга_Михайловна</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
-    </row>
-    <row r="23" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T22" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Обозова_Елизавета_Михайловна</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
-    </row>
-    <row r="24" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T23" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Обозова_Анна_Михайловна</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="T24" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Лебедев_Сергей_Михайлович</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G25" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="H25" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>275</v>
-      </c>
       <c r="J25" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="O25" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="T25" s="10"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -2199,13 +2288,13 @@
         <v>81</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2216,10 +2305,10 @@
         <v>81</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>4</v>
@@ -2233,10 +2322,10 @@
         <v>81</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>5</v>
@@ -2250,7 +2339,7 @@
         <v>81</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>86</v>
@@ -2267,7 +2356,7 @@
         <v>81</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>88</v>
@@ -3202,13 +3291,13 @@
         <v>219</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3222,7 +3311,7 @@
         <v>44</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>34</v>
@@ -3236,10 +3325,10 @@
         <v>219</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>35</v>
@@ -3253,13 +3342,13 @@
         <v>219</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -4439,6 +4528,42 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4456,7 +4581,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>223</v>
+        <v>332</v>
+      </c>
+      <c r="B2" t="s">
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -4523,14 +4651,14 @@
     </row>
     <row r="2" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="str">
-        <f>B2&amp;"__"&amp;C2</f>
+        <f t="shared" ref="A2:A7" si="0">B2&amp;"__"&amp;C2</f>
         <v>Обозов_Никита__Обозова_Ульяна</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>21</v>
@@ -4547,20 +4675,20 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
-        <f>B3&amp;"__"&amp;C3</f>
+        <f t="shared" si="0"/>
         <v>Кононов_Андрей_Николаевич__Обозова_Прасковья_Михайловна</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D3" t="s">
         <v>21</v>
       </c>
       <c r="J3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="K3" t="s">
         <v>31</v>
@@ -4568,14 +4696,14 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
-        <f>B4&amp;"__"&amp;C4</f>
+        <f t="shared" si="0"/>
         <v>Обозов_Михаил_Никититич__Агафья_Ивановна</v>
       </c>
       <c r="B4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>21</v>
@@ -4583,14 +4711,14 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="str">
-        <f>B5&amp;"__"&amp;C5</f>
+        <f t="shared" si="0"/>
         <v>Лебедев_Сергей_Михайлович__Кононова_Анна_Андреевна</v>
       </c>
       <c r="B5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D5" t="s">
         <v>21</v>
@@ -4602,14 +4730,14 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="str">
-        <f>B6&amp;"__"&amp;C6</f>
+        <f t="shared" si="0"/>
         <v>Кононов_Иван_Николаевич__Леонтьева_Мария_Петровна</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>21</v>
@@ -4618,14 +4746,14 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="str">
-        <f>B7&amp;"__"&amp;C7</f>
+        <f t="shared" si="0"/>
         <v>Кононов_Николай_Спиридонович__Сухарникова_Акулина</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>21</v>
@@ -5041,7 +5169,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2"/>
       <c r="C2" t="s">
@@ -5052,14 +5180,14 @@
         <v>Обозов_Михаил_Никититич__Агафья_Ивановна-.jpg</v>
       </c>
       <c r="E2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="I2"/>
       <c r="J2" s="2"/>
       <c r="L2"/>
       <c r="M2"/>
       <c r="N2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -5276,10 +5404,10 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C2" t="s">
         <v>39</v>
@@ -5289,23 +5417,23 @@
         <v>Обозова_Прасковья_Михайловна-max.jpg</v>
       </c>
       <c r="E2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G2"/>
       <c r="H2" s="2"/>
       <c r="J2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C3" t="s">
         <v>39</v>
@@ -5315,15 +5443,15 @@
         <v>Обозова_Прасковья_Михайловна-min.jpg</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G3"/>
       <c r="H3" s="2"/>
       <c r="J3" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -5457,10 +5585,10 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C2" t="s">
         <v>58</v>
@@ -5470,21 +5598,21 @@
         <v>Луки-Елпатьево-map.png</v>
       </c>
       <c r="E2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
       <c r="H2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N2"/>
     </row>
@@ -5562,10 +5690,10 @@
     </row>
     <row r="2" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>276</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>278</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>39</v>
@@ -5575,19 +5703,19 @@
         <v>Лебедев_Сергей_Михайлович-учетно_послужная_карточка.jpg</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
